--- a/rabbit-web-app/public/sample_excels/dispatch/shipper_bulk_sample.xlsx
+++ b/rabbit-web-app/public/sample_excels/dispatch/shipper_bulk_sample.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Shippers Bulk" sheetId="1" r:id="rId1"/>
+    <sheet name="Shippers" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,15 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
-  <cols>
-    <col min="1" max="1" width="35.83203125" customWidth="1"/>
-    <col min="2" max="2" width="50.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:G7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,15 +407,18 @@
         <v>address</v>
       </c>
       <c r="C1" t="str">
+        <v>email</v>
+      </c>
+      <c r="D1" t="str">
         <v>phone</v>
       </c>
-      <c r="D1" t="str">
-        <v>pinCode</v>
-      </c>
       <c r="E1" t="str">
+        <v>zipCode</v>
+      </c>
+      <c r="F1" t="str">
         <v>startTime</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>endTime</v>
       </c>
     </row>
@@ -435,15 +430,18 @@
         <v>Plot No. 45, Sector 18, Vashi, Navi Mumbai, Maharashtra</v>
       </c>
       <c r="C2" t="str">
-        <v>+91 98201 12345</v>
+        <v>vashi.hub@relianceretail.com</v>
       </c>
       <c r="D2" t="str">
+        <v>98201 12345</v>
+      </c>
+      <c r="E2" t="str">
         <v>400703</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>08:00 AM</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>06:00 PM</v>
       </c>
     </row>
@@ -455,101 +453,116 @@
         <v>NH-8, Near Toll Plaza, Mundra, Kutch, Gujarat</v>
       </c>
       <c r="C3" t="str">
-        <v>+91 98795 23456</v>
+        <v>mundra.dispatch@adaniagri.com</v>
       </c>
       <c r="D3" t="str">
+        <v>98795 23456</v>
+      </c>
+      <c r="E3" t="str">
         <v>370421</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>07:00 AM</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>07:00 PM</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Mahindra Logistics Fulfillment Center</v>
+        <v>Flipkart Instakart Fulfilment Centre</v>
       </c>
       <c r="B4" t="str">
-        <v>Survey No. 128, Chakan Industrial Area, Pune, Maharashtra</v>
+        <v>Warehouse Block C, Bilaspur-Tauru Road, Gurugram, Haryana</v>
       </c>
       <c r="C4" t="str">
-        <v>+91 91588 34567</v>
+        <v>fc.gurugram@flipkart.com</v>
       </c>
       <c r="D4" t="str">
-        <v>410501</v>
+        <v>98180 34567</v>
       </c>
       <c r="E4" t="str">
-        <v>08:30 AM</v>
+        <v>122413</v>
       </c>
       <c r="F4" t="str">
-        <v>05:30 PM</v>
+        <v>06:00 AM</v>
+      </c>
+      <c r="G4" t="str">
+        <v>10:00 PM</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Flipkart Instakart Logistics Hub</v>
+        <v>Amazon IN Sortation Centre</v>
       </c>
       <c r="B5" t="str">
-        <v>Plot 8-12, Bilaspur Industrial Area, Gurugram, Haryana</v>
+        <v>Bhiwandi Industrial Corridor, Mankoli Phata, Thane, Maharashtra</v>
       </c>
       <c r="C5" t="str">
-        <v>+91 99102 45678</v>
+        <v>bhiwandi.sort@amazon.in</v>
       </c>
       <c r="D5" t="str">
-        <v>122413</v>
+        <v>98210 45678</v>
       </c>
       <c r="E5" t="str">
-        <v>09:00 AM</v>
+        <v>421302</v>
       </c>
       <c r="F5" t="str">
-        <v>09:00 PM</v>
+        <v>24 Hours</v>
+      </c>
+      <c r="G5" t="str">
+        <v>24 Hours</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ITC North Warehouse &amp; Consignee</v>
+        <v>ITC Central Distribution Warehouse</v>
       </c>
       <c r="B6" t="str">
-        <v>Industrial Area, Phase 2, Baddi, Solan, Himachal Pradesh</v>
+        <v>ITC Park, Dhulagarh Industrial Hub, Howrah, West Bengal</v>
       </c>
       <c r="C6" t="str">
-        <v>+91 98160 56789</v>
+        <v>dhulagarh.cdc@itc.in</v>
       </c>
       <c r="D6" t="str">
-        <v>173205</v>
+        <v>98300 56789</v>
       </c>
       <c r="E6" t="str">
-        <v>08:00 AM</v>
+        <v>711302</v>
       </c>
       <c r="F6" t="str">
-        <v>05:00 PM</v>
+        <v>09:00 AM</v>
+      </c>
+      <c r="G6" t="str">
+        <v>06:00 PM</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Delhivery Express Distribution Facility</v>
+        <v>Tata Steel Logistics Yard</v>
       </c>
       <c r="B7" t="str">
-        <v>Soukya Road, Whitefield Industrial Area, Bengaluru, Karnataka</v>
+        <v>Gate 4, Jamshedpur Works, Jamshedpur, Jharkhand</v>
       </c>
       <c r="C7" t="str">
-        <v>+91 98450 67890</v>
+        <v>jspr.yard@tatasteel.com</v>
       </c>
       <c r="D7" t="str">
-        <v>560066</v>
+        <v>98351 67890</v>
       </c>
       <c r="E7" t="str">
+        <v>831001</v>
+      </c>
+      <c r="F7" t="str">
         <v>06:00 AM</v>
       </c>
-      <c r="F7" t="str">
-        <v>10:00 PM</v>
+      <c r="G7" t="str">
+        <v>08:00 PM</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
   </ignoredErrors>
 </worksheet>
 </file>